--- a/artfynd/A 46352-2024 artfynd.xlsx
+++ b/artfynd/A 46352-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120840651</v>
+        <v>120840649</v>
       </c>
       <c r="B2" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>880416</v>
+        <v>880378</v>
       </c>
       <c r="R2" t="n">
-        <v>7380227</v>
+        <v>7380072</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120840646</v>
+        <v>120840648</v>
       </c>
       <c r="B3" t="n">
-        <v>57459</v>
+        <v>78601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>880328</v>
+        <v>880316</v>
       </c>
       <c r="R3" t="n">
-        <v>7379998</v>
+        <v>7380008</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-03</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120840649</v>
+        <v>120840647</v>
       </c>
       <c r="B4" t="n">
-        <v>78598</v>
+        <v>57462</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>880378</v>
+        <v>879920</v>
       </c>
       <c r="R4" t="n">
-        <v>7380072</v>
+        <v>7380068</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -960,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-03</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>3 stycken</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120840648</v>
+        <v>120840645</v>
       </c>
       <c r="B5" t="n">
-        <v>78598</v>
+        <v>57367</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>880316</v>
+        <v>880109</v>
       </c>
       <c r="R5" t="n">
-        <v>7380008</v>
+        <v>7380214</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1062,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-03</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hackspår gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120840647</v>
+        <v>120840651</v>
       </c>
       <c r="B6" t="n">
-        <v>57459</v>
+        <v>78601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>879920</v>
+        <v>880416</v>
       </c>
       <c r="R6" t="n">
-        <v>7380068</v>
+        <v>7380227</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1164,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-03</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>3 stycken</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120840645</v>
+        <v>120840650</v>
       </c>
       <c r="B7" t="n">
-        <v>57364</v>
+        <v>78601</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>880109</v>
+        <v>880455</v>
       </c>
       <c r="R7" t="n">
-        <v>7380214</v>
+        <v>7380078</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1271,11 +1271,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-03</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hackspår gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120840650</v>
+        <v>120840646</v>
       </c>
       <c r="B8" t="n">
-        <v>78598</v>
+        <v>57462</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1314,25 +1309,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>880455</v>
+        <v>880328</v>
       </c>
       <c r="R8" t="n">
-        <v>7380078</v>
+        <v>7379998</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1378,6 +1373,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-11-03</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD8" t="b">
